--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_013/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_013/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -359,21 +364,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -489,6 +479,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -524,52 +519,12 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
     <comment ref="I6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="H7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="I7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1321,17 +1276,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>LEO Rideshare Avionics Shelf Bracket FEM (BRK-112A)</t>
+          <t>LEO Rideshare Avionics Bracket FEM (BRK-112A)</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Structural assessment of BRK-112A bracket under combined launch static loads and modal check</t>
+          <t>Structural adequacy assessment of BRK-112A bracket under combined launch loads and modal frequency requirement</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Linear-elastic finite element assessment of a machined 7075-T7351 aluminum L-bracket supporting an IMU and power converter on a LEO rideshare avionics shelf. The model is used to evaluate static stress margins under 20 g vertical and 12 g lateral combined acceleration, natural frequency (first bending/torsion &gt; 250 Hz), bolted interface slip, and contact behavior. Fatigue, thermal, and plasticity effects are deferred. Results support downselect and drawing release decisions.</t>
+          <t>Linear-elastic finite element analysis of a machined 7075-T7351 aluminum L-bracket supporting an IMU and power converter on a LEO rideshare avionics shelf. The model is used to demonstrate positive yield margin under combined 20g vertical and 12g lateral equivalent static loads, confirm first natural frequency above 250 Hz with attached masses, and evaluate bolted interface slip. Results support downselect and drawing release decisions.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1369,9 +1324,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (LEO rideshare avionics shelf bracket structural assessment report, Modeling lead L. D. Kim, Ansys Mechanical R2024.1, 2026 Q3, tag MECH-24Q3-BRK-07); supplemented by appendix.md</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1432,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1500,7 +1455,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Bracket must carry 20 g vertical and 12 g lateral launch loads with yield margin ≥ 1.25, first natural frequency &gt; 250 Hz with payload masses, negligible bolted interface slip under lateral acceleration, and positive margin against yielding at 25 C under combined load.</t>
+          <t>Bracket must carry 20g vertical and 12g lateral combined launch loads with a minimum yield design factor of 1.25; maintain first natural frequency above 250 Hz with attached payload masses; limit bolted interface slip to negligible levels under lateral acceleration</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1522,12 +1477,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>BRK-112A Ansys Mechanical FEM</t>
+          <t>BRK-112A Ansys FEM (Linear-Elastic Static + Modal)</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Nonlinear static and modal FEM in Ansys Mechanical R2024.1; 352k-element quadratic tetrahedral mesh; frictional contact at bolted interface; pretension elements for M6 bolts; distributed lumped masses for IMU and converter payloads.</t>
+          <t>Ansys Mechanical R2024.1 nonlinear static (pretension + contact) and Block Lanczos modal model of the 7075-T7351 L-bracket, medium mesh baseline (352k elements, SOLID187 quadratic tetrahedra)</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1494,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>MMPDS-17 Material Data for 7075-T7351</t>
+          <t>Bench Strain-Gage Test Data — TST-BRK112A-05-QL01</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Tensile and yield strength, elastic modulus, and density data for 7075-T7351 aluminum drawn from MMPDS-17 Table 3.7.2.0.1 and flight-lot billet certifications (E = 71.4–72.1 GPa, n=8 coupons).</t>
+          <t>Quasi-static bench test on single bracket article BRK-112A-05; two 120-ohm strain gauges under 2.50 kN vertical load; measured strains SG-1 = 820 µε, SG-2 = 410 µε with ±5 µε instrumentation accuracy and ±1% load cell uncertainty</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1511,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Bench Test Data TST-BRK112A-05-QL01</t>
+          <t>Material and Load Environment Inputs</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Quasi-static vertical bench load test on single bracket article (serial BRK-112A-05); two strain gauges (SG-1, SG-2) at 2.50 kN applied load; raw strain files, load cell calibration sheet, and gauge placement sketches archived.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Load Environments Note LE-26-031</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Bus-level combined acceleration envelope (20 g vertical, 12 g lateral) used to derive equivalent static loads applied in the FEM.</t>
+          <t>7075-T7351 material properties from MMPDS-17 and billet certification (E = 71.4–72.1 GPa, n=8 coupons); load levels from Load Environments note LE-26-031; geometry from STEP export BRK-112A_revD (CAD Team, 2026-05-07)</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2015,7 +1953,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Strain Gauge Correlation — Bench Test</t>
+          <t>Strain-Gage Physical Correlation</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2030,12 +1968,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Single machined bracket (BRK-112A-05) loaded quasi-statically to 2.50 kN vertical. Measured strains at SG-1 (820 µε) and SG-2 (410 µε) compared to FEA predictions of 780 µε and 435 µε respectively. Errors of -4.9% and +6.1% fall within combined measurement and modeling uncertainty bounds.</t>
+          <t>Predicted principal strains from FEA medium mesh compared to measured strains from quasi-static bench test on single bracket article under 2.50 kN vertical load at two strain-gage locations</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Physical bench test on production-equivalent machined article with calibrated load cell and vendor-calibrated strain gauges</t>
+          <t>Bench test data TST-BRK112A-05-QL01 (SG-1 = 820 µε, SG-2 = 410 µε)</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2045,12 +1983,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Instrumentation accuracy (±5 µε), load cell uncertainty (±1%), combined measurement and modeling uncertainty bounds discussed in Section 6</t>
+          <t>Instrumentation accuracy ±5 µε and load cell ±1% cited; combined measurement and modeling uncertainty bounds discussed qualitatively in report Section 6</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>SG-1 error -4.9%; SG-2 error +6.1%</t>
+          <t>SG-1 error -4.9% (predicted 780 µε vs measured 820 µε); SG-2 error +6.1% (predicted 435 µε vs measured 410 µε)</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2072,12 +2010,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Three mesh densities (coarse 176k, medium 352k, fine 798k elements) compared for peak von Mises stress, tip displacement, and bolt load distribution under combined g-load case. GCI computed for medium-to-fine transition.</t>
+          <t>Three-mesh sweep (coarse 176k, medium 352k, fine 798k elements) evaluating peak von Mises stress, tip displacement, and bolt load distribution convergence</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / generalized GCI asymptote estimate</t>
+          <t>Richardson extrapolation attempted; GCI-based index computed at medium-to-fine transition</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2087,12 +2025,12 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>Grid Convergence Index (GCI), effective order p = 1.8; medium-to-fine GCI = 3.8% for peak stress</t>
+          <t>Generalized Grid Convergence Index (GCI) with effective order p = 1.8; 3.8% for medium-to-fine stress; path-averaged readout 1 mm from fillet root to avoid singularity</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>GCI (medium→fine) = 3.8%; tip displacement within 0.6% medium vs fine; bolt load share within 0.2%</t>
+          <t>GCI (medium to fine) = 3.8%; tip displacement medium-to-fine change &lt; 1%; bolt load share medium-to-fine change &lt; 0.2%</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2104,7 +2042,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Modal Frequency Check</t>
+          <t>Latin Hypercube Uncertainty Propagation</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2114,22 +2052,27 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Block Lanczos eigenvalue extraction (12 modes) with distributed payload masses. First bending mode at 318 Hz and first torsion at 367 Hz both exceed the 250 Hz requirement with ≥27% headroom.</t>
+          <t>200-sample LHS propagating uncertainty in E, vertical g, lateral g, friction coefficient, and bolt preload through baseline medium-mesh model; tracking peak von Mises stress and maximum interface slip</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Design requirement of first natural frequency &gt; 250 Hz</t>
+          <t>Yield strength 503 MPa and slip threshold (negligible slip requirement)</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>Latin Hypercube Sampling (LHS), 200 draws, random seed 83427; distributions: Normal for E (COV 3%), Normal truncated for g-levels (COV 8%), Triangular for friction, Normal for bolt preload</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>First bending mode 318 Hz (27% margin above 250 Hz); first torsion 367 Hz</t>
+          <t>Peak stress mean 213 MPa, SD 18 MPa, 95th percentile 246 MPa (FOS vs yield at P95 = 2.05); slip 95th percentile &lt; 12 µm</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2141,7 +2084,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Latin Hypercube Uncertainty Propagation</t>
+          <t>Modal Frequency Check</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2151,67 +2094,25 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>200-sample LHS study propagating distributions in E, vertical g, lateral g, friction coefficient, and bolt preload through the baseline medium-mesh model. Peak von Mises stress and interface slip tracked across the sample space.</t>
+          <t>Block Lanczos extraction of 12 modes with distributed payload masses; first bending and torsion frequencies compared to 250 Hz requirement</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Yield strength of 503 MPa and slip limit for cable strain relief</t>
+          <t>Design requirement: first natural frequency &gt; 250 Hz</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Latin hypercube sampling (n=200), random seed 83427; 95th percentile reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Mean peak stress 213 MPa, SD 18 MPa, 95th percentile 246 MPa (&lt;50% of yield 503 MPa); 95th percentile slip &lt;12 µm</t>
+          <t>First bending mode 318 Hz (27% margin above 250 Hz); first torsion 367 Hz</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Baseplate Compliance Sensitivity Check</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>ValidationResult</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Fixed-support baseline compared to submodel with explicit 8 mm deck plate and ribs. Peak stress changed by +1.7% and first bending frequency reduced by 6 Hz, both within the convergence and property uncertainty envelope.</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Baseline fixed-boundary FEM</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>Peak stress change +1.7%; frequency change -6 Hz (318→312 Hz, still &gt;250 Hz requirement)</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2362,12 +2263,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented quality processes; version identified and archived</t>
+          <t>Commercial solver with documented version control and identifiable build used; model files archived under version-tagged repository</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Ansys Mechanical R2024.1 is a widely certified commercial FEA solver. The exact solver build is recorded in the project repository under tag MECH-24Q3-BRK-07 alongside all model files and postprocessing macros, supporting reproducibility. No explicit ISO quality certificate or regression test results are cited in the documents, but commercial solver status and version traceability are documented.</t>
+          <t>Ansys Mechanical R2024.1 is a commercial, widely validated FEA solver. The report identifies the specific release (R2024.1) and solver build. All model files, geometry cleanup scripts, contact definitions, and parameterized load templates are archived in the mission repository under tag MECH-24Q3-BRK-07. The sampling study records the exact solver build and random seed (83427). No explicit regression test suite or ISO 9001 documentation is cited, limiting the level to 3.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2396,12 +2297,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Evidence that code correctly solves governing equations for linear elasticity and eigenvalue problems</t>
+          <t>Code has been applied to benchmark or analytical problems demonstrating correct equation solving; or reliance on established commercial solver documentation</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Ansys Mechanical's SOLID187 element and Block Lanczos eigensolver are industry-standard and widely benchmarked in the literature. No project-specific analytical solution comparisons or MMS studies are reported. Reliance is on the commercial solver's established verification pedigree. Achieved level reflects this indirect evidence without project-specific code verification activities.</t>
+          <t>The report relies on Ansys Mechanical R2024.1 as a well-established commercial code. No explicit MMS studies, analytical benchmark comparisons, or internal code verification activities are documented within this study. The commercial code's reputation and specific version identification provide basic evidence. Level 2 reflects reliance on the solver's inherent verification status without project-specific code verification activities.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2430,12 +2331,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with quantified discretization uncertainty; baseline mesh within acceptable error of asymptote</t>
+          <t>Mesh convergence demonstrated across at least three refinement levels with a quantified convergence index for the primary QoI</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three meshes (176k, 352k, 798k elements) with coarse, medium, and fine densities were evaluated. A generalized GCI of 3.8% was computed for medium-to-fine transition at effective order p=1.8 for peak stress. Tip displacement and bolt load shares are within 1% between medium and fine. Contact-driven non-monotonicity noted and hotspot path placed 1 mm from fillet root to mitigate singularity effects. Richardson extrapolation not applied due to non-monotonicity, slightly limiting the upper bound of rigor.</t>
+          <t>Three meshes (coarse 176k, medium 352k, fine 798k elements) were studied. Peak von Mises stress, tip displacement, and bolt load distribution were tracked. A generalized GCI of 3.8% was computed for the medium-to-fine transition at effective order p = 1.8. Displacements and bolt forces are within 1% between medium and fine. Stress readout is path-averaged 1 mm from the fillet root to mitigate singularity effects. Monotonicity of stress is imperfect due to contact patch evolution; Richardson extrapolation was not applied, capping the level at 3.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2464,12 +2365,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Solver convergence criteria documented; residuals and contact stability confirmed</t>
+          <t>Convergence criteria documented and achieved; contact stabilization verified; residuals within acceptable tolerances</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Force residuals confirmed &lt;0.2% of applied load for static runs. Contact chattering eliminated via normal stiffness capping. Maximum contact penetration 2.3 µm at outer corner, within 0.5% element edge guideline. Geometric nonlinearity shown to contribute &lt;1.5% change in hotspot stress (&lt;0.03 mm deflection), justifying linear analysis. Iteration histories and solver settings archived in mission repository.</t>
+          <t>Force residuals held below 0.2% of applied load. Contact chattering was eliminated via normal stiffness capping. Augmented Lagrange contact with penetration tolerance set to 0.5% of element edge length. Maximum penetration 2.3 microns at the outer corner (appendix A7), within the 0.5% element edge guideline. Stick-slip transition isolated with no oscillatory chatter after normal stiffness tuning. Geometric nonlinearity shown to contribute &lt;1.5% change in hotspot stress; turned off for efficiency with documented justification. Solver convergence criteria matched the baseline for all 200 LHS samples.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2498,12 +2399,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Boundary conditions and model setup independently verifiable; mesh quality documented; postprocessing reproducible</t>
+          <t>Independent review or systematic checking of boundary conditions, load application, contact definitions, and postprocessing</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Geometry source traced to STEP export BRK-112A_revD with documented cleanup script. Mesh quality metrics reported (Jacobian ratio, aspect ratio) for all three meshes. Boundary condition sensitivity (fixed vs. spring-supported base) checked. Postprocessing macros (pp_brk_hotspot.mac, pp_modes_brk12.mac) archived to reduce operator-dependent variability. All model files archived under tag MECH-24Q3-BRK-07. No formal independent reviewer is named, which limits achievement above level 3.</t>
+          <t>Boundary conditions are explicitly documented and justified: baseplate fixed constraint validated by spring submodel trial (&lt;1% stress change), bolt pretension sections calibrated to shank stiffness, payload masses located per vendor drawings. A pretest FEA map was used to orient strain gauges, demonstrating model setup was checked before test. Contact definitions and geometry cleanup scripts are archived and described in detail. An auxiliary submodel analysis confirmed the baseplate rigidity assumption. No formal independent third-party review is documented, which limits the level to 3.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2532,12 +2433,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and modeling idealizations documented and justified for the physics regime</t>
+          <t>Governing equations and key modeling choices (contact, material model, boundary conditions) justified relative to the physical phenomena being captured; known limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Linear-elastic isotropic constitutive model justified by large margins to yield (FOS 2.50 vs. 1.25 required) and demonstrated &lt;1.5% geometric nonlinearity influence. Contact modeled as frictional surface-to-surface with Augmented Lagrange. Fastener representation via pretension elements with calibrated shank stiffness is documented. Payload masses as distributed lumped masses is standard for this class of problem. Limitations (no plasticity, no fatigue, no thermal) explicitly documented in Sections 7–8.</t>
+          <t>Linear-elastic isotropic material model is appropriate and justified for aluminum below yield (FOS &gt; 2.0). Large-deflection nonlinearity shown to contribute &lt;1.5% and is excluded with documented justification. Frictional contact with augmented Lagrange formulation is used for the bolted interface; friction sensitivity (μ = 0.10–0.40) is explored. Thread omission is explicitly justified and mitigated by pretension element calibration. Baseplate rigidity is justified by stiffness ratio and corroborated by submodel. Known limitations (no plasticity, no fatigue, no thermal, no dynamic environment) are explicitly catalogued in Section 8.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2566,12 +2467,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties, loads, and geometry traceable to qualified sources with characterised uncertainty</t>
+          <t>Material properties traceable to recognized standards or test data; load inputs traceable to environment specification; geometry from controlled CAD source; input uncertainties characterized</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Material properties (E, Sy, Su, ν, density) drawn from MMPDS-17 and flight-lot billet certifications (n=8 coupons, E = 71.4–72.1 GPa). Load levels trace to LE-26-031. Geometry from CAD STEP BRK-112A_revD. Input uncertainty ranges defined for LHS study (COV 3% on E, COV 8% on g-levels, triangular distribution on μ, normal on bolt preload). Poisson's ratio not directly measured from the billet; density taken from handbook — minor gap preventing level 4.</t>
+          <t>Material properties (E = 71.7 GPa, ν = 0.33, Sy = 503 MPa) from MMPDS-17 Table 3.7.2.0.1 and AMS 4124, with modulus distribution supported by billet certification data (E = 71.4–72.1 GPa, n=8 coupons, COV ~2–3%). Geometry from STEP export BRK-112A_revD (CAD Team, 2026-05-07). Load levels from LE-26-031. Payload masses and CG offsets from vendor drawings. Input uncertainty distributions are defined for the LHS study (E, g-levels, friction, bolt preload). Poisson's ratio and density are handbook values without measured uncertainty, and material yield variance is acknowledged but not included in the LHS, capping the level at 3.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2600,12 +2501,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article is production-representative; sample size and characteristics documented</t>
+          <t>Test articles are production-representative; sample size is adequate for the validation purpose</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>One machined bracket (serial BRK-112A-05) was tested. The report confirms it is a machined article consistent with the flight design. Sample size of n=1 is the primary limitation; no statistical characterization across multiple specimens is performed. The report acknowledges this limitation explicitly (Section 8) and notes additional spot-checks are recommended but not scheduled.</t>
+          <t>Only a single bracket article (serial BRK-112A-05) was tested in the bench load check. The report acknowledges this explicitly in Section 8 (limited test scope) and recommends additional spot-checks if a second part becomes available. No statistical characterization of article-to-article variability is possible with n=1. The article is described as machined to drawing, making it nominally production-representative, but the limited sample size is a recognized gap.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2630,16 +2531,16 @@
         <v>2</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions measured and controlled; instrumentation calibrated; measurement uncertainty reported</t>
+          <t>Test conditions documented with calibrated instrumentation; measurement uncertainties quantified; boundary conditions representative of the modeled case</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Calibrated load cell (±1% accuracy) and vendor-calibrated 120-ohm strain gauges (gauge factor provided; ±5 µε instrumentation accuracy) were used. Base clamped to steel platen with through-bolts. Load applied via clevis at the IMU mounting pattern centroid. Test notes, raw strain files, and load cell calibration sheet archived (TST-BRK112A-05-QL01). Test setup does not replicate lateral load or flight baseplate threads — documented as a known limitation. Environmental conditions (temperature) not explicitly reported but implied as room temperature.</t>
+          <t>The bench test used calibrated 120-ohm strain gauges with vendor-provided gage factors and a load cell with ±1% accuracy. Instrumentation accuracy of ±5 µε is documented. Load application via clevis at the IMU mounting pattern centroid is described. A load cell calibration sheet was appended to the test notes (TST-BRK112A-05-QL01). Boundary condition differences from flight (through-bolts to steel platen vs. flight baseplate, no lateral load, non-representative thread engagement) are explicitly acknowledged and their effect on the targeted load path is discussed.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2661,19 +2562,19 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions and inputs matched to test conditions; differences identified and their effect bounded</t>
+          <t>Model boundary conditions and loads set to match the experimental test configuration; differences between test and model identified and assessed</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Model run under same boundary conditions as bench test (vertical load 2.50 kN, room temperature, same material properties). Known differences identified: platen threads not representative of flight baseplate; no lateral load in test. Effect of the boundary condition difference assessed via Section 6.1 submodel (deck compliance adds &lt;1.7% stress change). The absence of lateral load in the test limits equivalency for the combined-load regime, which is the primary design case. Measurement uncertainty (±5 µε, ±1% load) is acknowledged. Full propagation of test input uncertainty into the comparison is not formally quantified.</t>
+          <t>The FEA model was re-run under the bench test boundary and load conditions (2.50 kN vertical, same footprint constraint, room temperature, E per Section 2.3) for the strain comparisons. The main configuration differences — steel platen vs. flight baseplate, omission of lateral load, non-modeled thread engagement — are explicitly documented. The report argues the vertical bending-dominated state exercises the primary stiffness and hotspot, providing partial equivalency. However, the differences are not propagated quantitatively into uncertainty bounds for the validation comparison, limiting the level to 2.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2702,12 +2603,12 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison of model predictions to measurements at multiple locations; errors within combined uncertainty bounds</t>
+          <t>Quantitative comparison between model predictions and experimental measurements at multiple points; errors within combined uncertainty bounds</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Two strain gauge locations compared: SG-1 error -4.9%, SG-2 error +6.1%. Both errors stated to be within combined measurement and modeling uncertainty bounds. Tip displacement and bolt load distributions additionally tracked across meshes (internal consistency). Modal frequencies compared to design requirement. LHS 95th-percentile results reported. Correlation is limited to two strain points under one load direction, which constrains depth of comparison, but the quantitative reporting and uncertainty framing are adequate for the MRL.</t>
+          <t>Quantitative strain comparisons at two gage locations: SG-1 error -4.9% (780 µε predicted vs 820 µε measured), SG-2 error +6.1% (435 µε predicted vs 410 µε measured). Both errors are stated to fall within combined measurement and modeling uncertainty bounds. Predicted vs measured strains are tabulated with measurement uncertainty (±5 µε, ±1% load cell). Comparison is limited to two points under one load configuration (vertical only, no lateral), and the report acknowledges this scope limitation. Multiple QoIs (stress, displacement, bolt load share, modal frequencies) are tracked computationally but only strains are compared against physical measurements.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2732,16 +2633,16 @@
         <v>3</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly address the safety and performance requirements of the COU; measurable both computationally and experimentally</t>
+          <t>Model outputs directly address the decision-driving performance and safety requirements; QoIs are measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>QoIs (peak von Mises stress, safety factor vs. yield, natural frequencies, interface slip magnitude, tip deflection) directly map to the four stated bracket requirements (yield margin ≥ 1.25, frequency &gt; 250 Hz, negligible slip, load path fidelity). Strain gauge measurements provide an experimentally accessible proxy for stress. Modal frequencies are directly computable and design-requirement-referenced. Fatigue and thermal QoIs are explicitly deferred with documented rationale.</t>
+          <t>The QoIs — peak von Mises stress (yielding margin), tip displacement, bolt interface slip, and first natural frequency — directly correspond to each stated performance requirement (yield FOS ≥ 1.25, frequency ≥ 250 Hz, negligible slip). The strain-gage physical check targets the same hotspot region as the peak stress QoI, confirming the computational metric is physically accessible. The LHS propagates uncertainty directly through these same QoIs to the P95 level. The mapping from QoIs to requirements is explicit and complete for the in-scope load cases.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2770,12 +2671,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions (geometry, load path, boundary conditions) sufficiently match the flight COU; coverage gaps identified and bounded</t>
+          <t>Validation conditions (loads, geometry, boundary conditions, environment) sufficiently represent the intended use; gaps identified and bounded</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation bench test used the actual flight-design machined bracket under a representative vertical load path, exercising the primary hotspot location. However, the test covered only the vertical load branch (not the combined 20 g vertical + 12 g lateral COU), used a non-representative baseplate boundary (platen with through-bolts, not flight deck threads), and tested only one article. These gaps are explicitly documented in Sections 4, 7, and 8. The LHS study partially compensates by bracketing load variability analytically. Deck compliance and coupled lateral response remain unvalidated experimentally, limiting this factor to level 2 despite the acknowledged and bounded gap.</t>
+          <t>The bench test exercises only the vertical load path on one article, using a steel platen fixture rather than the flight deck, with no lateral load and no pretension in the flight configuration. The flight COU requires combined 20g vertical and 12g lateral with the aluminum deck baseplate. The modal check is purely analytical with no experimental modal correlation. Gaps are honestly documented in Sections 7 and 8. The sensitivity and LHS studies extend confidence beyond the single validation point, but the direct validation coverage of the combined-load and lateral-load regime is absent. Deck compliance (deferred to CDR) could affect the 250 Hz modal requirement.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2960,7 +2861,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The BRK-112A FEM demonstrates adequate credibility for the current gate decision (downselect and drawing release) under the stated context of use (room-temperature linear-elastic static and modal assessment). The computed factor of safety against yield is 2.50 against a requirement of 1.25; the first natural frequency is 318 Hz with 27% margin above the 250 Hz requirement; interface slip remains below 7 µm nominal and below 12 µm at the 95th percentile. Strain gauge correlation errors of -4.9% and +6.1% are within combined uncertainty bounds. Mesh discretization uncertainty is bounded at ~4% GCI for peak stress. A 200-sample LHS study confirms robustness under plausible input scatter. Acceptance is subject to the following conditions: (1) manufacturing drawings must specify a minimum 2.0 mm fillet radius at the rib-base intersection; (2) a modal and combined-load check using the integrated deck FEM shall be completed before CDR to confirm frequency placement and stress levels with global flexibility; (3) fatigue, thermal, and plasticity assessments remain open and must be addressed in subsequent analysis cycles; (4) if a second article becomes available, an opportunistic lateral-load bench check is recommended to improve validation coverage of the combined-load regime.</t>
+          <t>The BRK-112A FEM demonstrates a yield factor of safety of 2.50 against the 1.25 minimum (P95 FOS ≥ 2.05 under combined input scatter), a first natural frequency of 318 Hz against the 250 Hz floor (27% margin), and bolted interface slip well below the negligible threshold under all sampled conditions. Physical bench correlation errors of -4.9% and +6.1% at two strain locations are within combined measurement and modeling uncertainty bounds. A 3.8% GCI confirms adequate mesh resolution. Model is accepted for downselect and drawing release subject to the following conditions: (1) minimum 2.0 mm fillet maintained at the rib-base intersection per drawing callout; (2) a quick modal and combined-load check using the integrated deck model shall be completed before CDR to confirm mode placement with bus-level flexibility; (3) fatigue, thermal, and manufacturing tolerance analyses remain open and must be addressed in subsequent increments before final flight certification.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2975,7 +2876,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
